--- a/P2Dmodel/OCP/OCP_from_LiionDB.xlsx
+++ b/P2Dmodel/OCP/OCP_from_LiionDB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailscuteducn-my.sharepoint.com/personal/202110182474_mail_scut_edu_cn/Documents/Code/Battery/P2Dmodel/OCP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59D6CA49-9B72-4F77-A050-BB4865903AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{59D6CA49-9B72-4F77-A050-BB4865903AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{032220A5-C578-4771-A8B3-3D497368316F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="833" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="833" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graphite_6_Ecker2015" sheetId="4" r:id="rId1"/>
@@ -56,14 +56,14 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="3">
   <si>
-    <t>θ</t>
+    <t>θs</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>OCP</t>
+    <t>UOCP</t>
   </si>
   <si>
-    <t>OCP</t>
+    <t>UOCP</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3402,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -4224,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5601,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -6040,7 +6040,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -6622,7 +6622,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -7300,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -7375,7 +7375,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -7735,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -9682,7 +9682,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -9848,6 +9848,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11601,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
